--- a/data.mn/public/datasets/mongolbank-exchange-rates-annual-average-major.xlsx
+++ b/data.mn/public/datasets/mongolbank-exchange-rates-annual-average-major.xlsx
@@ -467,13 +467,9 @@
       <c r="A2" t="n">
         <v>1993</v>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>3.55</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>295.26</v>
       </c>
@@ -485,14 +481,12 @@
       <c r="B3" t="n">
         <v>48.6</v>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
         <v>4.12</v>
       </c>
       <c r="E3" t="n">
         <v>0.12</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>409.25</v>
       </c>
@@ -504,14 +498,12 @@
       <c r="B4" t="n">
         <v>56.94</v>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
         <v>4.63</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>447.62</v>
       </c>
@@ -523,7 +515,6 @@
       <c r="B5" t="n">
         <v>72.70999999999999</v>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
         <v>5.42</v>
       </c>
@@ -544,7 +535,6 @@
       <c r="B6" t="n">
         <v>95.78</v>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
         <v>6.56</v>
       </c>
@@ -565,7 +555,6 @@
       <c r="B7" t="n">
         <v>101.92</v>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
         <v>6.47</v>
       </c>
@@ -1205,22 +1194,22 @@
         <v>2026</v>
       </c>
       <c r="B35" t="n">
-        <v>522.98</v>
+        <v>524.42</v>
       </c>
       <c r="C35" t="n">
-        <v>4157.14</v>
+        <v>4155.24</v>
       </c>
       <c r="D35" t="n">
-        <v>22.52</v>
+        <v>22.57</v>
       </c>
       <c r="E35" t="n">
-        <v>46.15</v>
+        <v>45.72</v>
       </c>
       <c r="F35" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="G35" t="n">
-        <v>3575.12</v>
+        <v>3577.38</v>
       </c>
     </row>
   </sheetData>
@@ -1290,10 +1279,6 @@
       <c r="B2" t="n">
         <v>295.26</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>3.55</v>
       </c>
@@ -1305,8 +1290,6 @@
       <c r="B3" t="n">
         <v>409.25</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>0.12</v>
       </c>
@@ -1324,8 +1307,6 @@
       <c r="B4" t="n">
         <v>447.62</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>0.1</v>
       </c>
@@ -1346,7 +1327,6 @@
       <c r="C5" t="n">
         <v>0.74</v>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>0.11</v>
       </c>
@@ -1367,7 +1347,6 @@
       <c r="C6" t="n">
         <v>0.84</v>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>0.14</v>
       </c>
@@ -1388,7 +1367,6 @@
       <c r="C7" t="n">
         <v>0.61</v>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>101.59</v>
       </c>
@@ -2025,22 +2003,22 @@
         <v>2026</v>
       </c>
       <c r="B35" t="n">
-        <v>3575.12</v>
+        <v>3577.38</v>
       </c>
       <c r="C35" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="D35" t="n">
-        <v>4157.14</v>
+        <v>4155.24</v>
       </c>
       <c r="E35" t="n">
-        <v>46.15</v>
+        <v>45.72</v>
       </c>
       <c r="F35" t="n">
-        <v>522.98</v>
+        <v>524.42</v>
       </c>
       <c r="G35" t="n">
-        <v>22.52</v>
+        <v>22.57</v>
       </c>
     </row>
   </sheetData>
